--- a/app/reports/TWN_research.xlsx
+++ b/app/reports/TWN_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>85.8</v>
+        <v>84.14</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5742039.347319348</v>
+        <v>5742039.077727597</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>85.8</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>492666976</v>
+        <v>483135168</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>323048640</v>
+        <v>324004384</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>23.045456</v>
+        <v>23.113636</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C8" s="32" t="n"/>
       <c r="D8" s="33" t="n">
-        <v>21.360434</v>
+        <v>20.897131</v>
       </c>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="33" t="n"/>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>371911392</v>
+        <v>377067872</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>4.7685947</v>
+        <v>4.8347106</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n"/>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>268185728</v>
+        <v>270200288</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>3.5032895</v>
+        <v>3.5296052</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n">

--- a/app/reports/TWN_research.xlsx
+++ b/app/reports/TWN_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-28 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>84.14</v>
+        <v>82.0001</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04647000312805176</v>
+        <v>0.04595999717712403</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5742039.077727597</v>
+        <v>5807155.064445043</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>84.14</v>
+        <v>82.0001</v>
       </c>
     </row>
     <row r="38">
@@ -1508,14 +1508,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>483135168</v>
+        <v>476187296</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n">
-        <v>73.3</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="6">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>324004384</v>
+        <v>324960128</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>23.113636</v>
+        <v>23.181818</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C7" s="32" t="n"/>
       <c r="D7" s="33" t="n">
-        <v>21.544998</v>
+        <v>21.690617</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C8" s="32" t="n"/>
       <c r="D8" s="33" t="n">
-        <v>20.897131</v>
+        <v>20.866182</v>
       </c>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="33" t="n"/>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>377067872</v>
+        <v>377789792</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>4.8347106</v>
+        <v>4.8439665</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>374390144</v>
+        <v>371335040</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>5.938326</v>
+        <v>5.889868</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>23.700165</v>
+        <v>23.81081</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>13.921013</v>
+        <v>14.024039</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>270200288</v>
+        <v>267395040</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>3.5296052</v>
+        <v>3.4929605</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n">
-        <v>41.879</v>
+        <v>42.154</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TWN_research.xlsx
+++ b/app/reports/TWN_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-28 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>82.0001</v>
+        <v>78.09</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04595999717712403</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5807155.064445043</v>
+        <v>5742038.775771545</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>82.0001</v>
+        <v>78.09</v>
       </c>
     </row>
     <row r="38">
@@ -1508,14 +1508,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>476187296</v>
+        <v>448395808</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n">
-        <v>72.62</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>324960128</v>
+        <v>321455680</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>23.181818</v>
+        <v>22.931818</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C7" s="32" t="n"/>
       <c r="D7" s="33" t="n">
-        <v>21.690617</v>
+        <v>21.526007</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C8" s="32" t="n"/>
       <c r="D8" s="33" t="n">
-        <v>20.866182</v>
+        <v>20.912605</v>
       </c>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="33" t="n"/>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>377789792</v>
+        <v>372878240</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>4.8439665</v>
+        <v>4.7809916</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>371335040</v>
+        <v>369404768</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>5.889868</v>
+        <v>5.859251</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>23.81081</v>
+        <v>23.974566</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>14.024039</v>
+        <v>14.201246</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>267395040</v>
+        <v>267178464</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>3.4929605</v>
+        <v>3.4901316</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n">
-        <v>42.154</v>
+        <v>41.564</v>
       </c>
     </row>
     <row r="15">
